--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M252"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1401,11 +1401,7 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -1523,11 +1519,7 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -1825,7 +1817,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1950,11 +1942,7 @@
           <t>Hospital de Constitución</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -2194,11 +2182,7 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -2435,7 +2419,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2547,7 +2531,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3475,11 +3459,7 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -3536,11 +3516,7 @@
           <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -4021,7 +3997,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4878,11 +4854,7 @@
           <t>Hospital  Lonquimay</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -4936,7 +4908,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5244,11 +5216,7 @@
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -5363,7 +5331,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5912,7 +5880,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5941,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6342,11 +6310,7 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -6522,7 +6486,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6644,7 +6608,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6669,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6730,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6791,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7376,7 +7340,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7401,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7562,11 +7526,7 @@
           <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -7620,7 +7580,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7641,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7702,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7806,11 +7766,7 @@
           <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -8233,11 +8189,7 @@
           <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -8352,7 +8304,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8657,7 +8609,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8782,11 +8734,7 @@
           <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -9026,11 +8974,7 @@
           <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -9087,11 +9031,7 @@
           <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -9755,7 +9695,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9816,7 +9756,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9877,7 +9817,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10060,7 +10000,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10061,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10426,7 +10366,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10548,7 +10488,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10549,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10670,7 +10610,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10978,11 +10918,7 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -11283,11 +11219,7 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -11768,7 +11700,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11829,7 +11761,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12165,7 +12097,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>617807-913-CM25</t>
+          <t>585-14-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12190,17 +12122,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12220,7 +12152,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>15667.62</v>
+        <v>23465.47</v>
       </c>
     </row>
     <row r="194">
@@ -12259,11 +12191,7 @@
           <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -12348,7 +12276,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>585-14-CM25</t>
+          <t>617807-913-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,17 +12301,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12403,7 +12331,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>23465.47</v>
+        <v>15667.62</v>
       </c>
     </row>
     <row r="197">
@@ -12442,11 +12370,7 @@
           <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -12470,7 +12394,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3779-5-CM25</t>
+          <t>1621-22-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12490,22 +12414,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.130.401-9</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12525,7 +12449,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>387.31</v>
+        <v>7742.05</v>
       </c>
     </row>
     <row r="199">
@@ -12836,7 +12760,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1621-22-CM25</t>
+          <t>3779-5-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,22 +12780,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>69.130.401-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12891,7 +12815,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7742.05</v>
+        <v>387.31</v>
       </c>
     </row>
     <row r="205">
@@ -13296,11 +13220,7 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -13507,7 +13427,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1407-15059-CM25</t>
+          <t>1402-56-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,7 +13452,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -13542,7 +13462,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13562,13 +13482,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>15119.9</v>
+        <v>10079.93</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3385-8-CM25</t>
+          <t>1407-15059-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13593,17 +13513,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13623,13 +13543,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3109.66</v>
+        <v>15119.9</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3481-15-CM25</t>
+          <t>3385-8-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13654,17 +13574,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13684,13 +13604,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>499.91</v>
+        <v>3109.66</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2080-5931-CM25</t>
+          <t>3481-15-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13715,17 +13635,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13745,13 +13665,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2015.99</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3428-19-CM25</t>
+          <t>2080-5931-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,17 +13696,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13806,13 +13726,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3241.71</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1968-131-CM25</t>
+          <t>3428-19-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,12 +13757,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13867,13 +13787,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>36287.76</v>
+        <v>3241.71</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3374-1-CM25</t>
+          <t>1968-131-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13898,17 +13818,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13928,13 +13848,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2015.99</v>
+        <v>36287.76</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1402-56-CM25</t>
+          <t>3374-1-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13959,12 +13879,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13989,13 +13909,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10079.93</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3160-10-CM25</t>
+          <t>977274-1-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14020,19 +13940,15 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.102.003-1</t>
+          <t>61.999.190-7</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -14050,13 +13966,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2203.34</v>
+        <v>1996.46</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>977274-1-CM25</t>
+          <t>1965-48-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14081,17 +13997,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.999.190-7</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14111,13 +14027,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1996.46</v>
+        <v>7985.85</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1965-48-CM25</t>
+          <t>1643-408-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14142,19 +14058,15 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -14172,7 +14084,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7985.85</v>
+        <v>10453.51</v>
       </c>
     </row>
     <row r="226">
@@ -14239,7 +14151,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1643-408-CM25</t>
+          <t>752-40-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14259,22 +14171,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14294,7 +14206,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>10453.51</v>
+        <v>1350.59</v>
       </c>
     </row>
     <row r="228">
@@ -14381,7 +14293,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14422,7 +14334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1371-7-CM25</t>
+          <t>3160-10-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14447,17 +14359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>61.102.003-1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14477,13 +14389,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>609.72</v>
+        <v>2203.34</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1202512-8-CM25</t>
+          <t>1371-7-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14508,17 +14420,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14538,13 +14450,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>9806.969999999999</v>
+        <v>609.72</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1391-174-CM25</t>
+          <t>1202512-9-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14569,17 +14481,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14599,13 +14511,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7064</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1978-128-CM25</t>
+          <t>1391-174-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14625,17 +14537,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14660,13 +14572,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>43135.01</v>
+        <v>7064</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>507428-2452-CM25</t>
+          <t>1978-128-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14686,22 +14598,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14721,13 +14633,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>26569.88</v>
+        <v>43135.01</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1628-11-CM25</t>
+          <t>507428-2452-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14752,17 +14664,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14782,13 +14694,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>12109.71</v>
+        <v>26569.88</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1202512-9-CM25</t>
+          <t>1628-11-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14813,17 +14725,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14843,13 +14755,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>284.4</v>
+        <v>12109.71</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>622134-9-CM25</t>
+          <t>1202512-8-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14874,17 +14786,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.979.920-8</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14904,13 +14816,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1438.03</v>
+        <v>9806.969999999999</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1288-40-CM25</t>
+          <t>622134-9-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14935,12 +14847,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.979.920-8</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14965,13 +14877,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>38347.43</v>
+        <v>1438.03</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1529-28-CM25</t>
+          <t>1288-40-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14996,17 +14908,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15026,13 +14938,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>42326.03</v>
+        <v>38347.43</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2205-5-CM25</t>
+          <t>1529-28-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15047,7 +14959,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15057,12 +14969,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15087,13 +14999,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5720.57</v>
+        <v>42326.03</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1681-64-CM25</t>
+          <t>2205-5-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,17 +15030,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15148,13 +15060,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>36280.94</v>
+        <v>5720.57</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1681-63-CM25</t>
+          <t>1681-64-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15187,11 +15099,7 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -15209,13 +15117,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>24828.26</v>
+        <v>36280.94</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1057543-4819-CM25</t>
+          <t>1681-63-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15235,22 +15143,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15270,13 +15178,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>57686.46</v>
+        <v>24828.26</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>652-33-CM25</t>
+          <t>1057543-4819-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15296,24 +15204,20 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -15331,13 +15235,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>27329.54</v>
+        <v>57686.46</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3431-13-CM25</t>
+          <t>652-33-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15362,17 +15266,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15392,13 +15296,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4576.46</v>
+        <v>27329.54</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3311-8-CM25</t>
+          <t>3431-13-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15423,17 +15327,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15453,13 +15357,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>55662.34</v>
+        <v>4576.46</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1079596-5-CM25</t>
+          <t>3311-8-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15484,17 +15388,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15514,13 +15418,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>21177.67</v>
+        <v>55662.34</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3374-5-CM25</t>
+          <t>1079596-5-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15545,17 +15449,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15575,13 +15479,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4553.58</v>
+        <v>21177.67</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4100-1-CM25</t>
+          <t>3374-5-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15606,17 +15510,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15636,13 +15540,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>7516.07</v>
+        <v>4553.58</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1661-62-CM25</t>
+          <t>4100-1-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15667,17 +15571,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15697,13 +15601,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>16017.61</v>
+        <v>7516.07</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5827-10-CM25</t>
+          <t>1661-62-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15728,17 +15632,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.977.660-7</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15758,13 +15662,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>202.41</v>
+        <v>16017.61</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057736-11-CM25</t>
+          <t>5827-10-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15784,22 +15688,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.977.660-7</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15819,6 +15723,67 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
+        <v>202.41</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1057736-11-CM25</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="n">
         <v>4213.13</v>
       </c>
     </row>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1412,7 +1468,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1473,7 +1533,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1530,7 +1594,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1591,7 +1659,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1652,7 +1724,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1713,7 +1789,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1774,7 +1854,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1835,7 +1919,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1896,7 +1984,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1953,7 +2045,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2014,7 +2110,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2075,7 +2175,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2136,7 +2240,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2193,7 +2301,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2254,7 +2366,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2315,7 +2431,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2376,7 +2496,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2437,7 +2561,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2498,7 +2626,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2559,7 +2691,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2620,7 +2756,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2681,7 +2821,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2742,7 +2886,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2803,7 +2951,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2864,7 +3016,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2925,7 +3081,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2986,7 +3146,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3047,7 +3211,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3108,7 +3276,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3169,7 +3341,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3230,7 +3406,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3291,7 +3471,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3352,7 +3536,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3413,7 +3601,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3470,7 +3662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3527,7 +3723,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3588,7 +3788,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3649,7 +3853,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3710,7 +3918,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3771,7 +3983,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3832,7 +4048,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3893,7 +4113,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3954,7 +4178,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4015,7 +4243,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4076,7 +4308,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4137,7 +4373,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4198,7 +4438,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4259,7 +4503,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4320,7 +4568,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4381,7 +4633,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4442,7 +4698,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4503,7 +4763,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4564,7 +4828,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4625,7 +4893,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4686,7 +4958,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4747,7 +5023,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4808,7 +5088,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4865,7 +5149,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4926,7 +5214,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4987,7 +5279,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5048,7 +5344,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5109,7 +5409,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5170,7 +5474,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5227,7 +5535,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5288,7 +5600,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5349,7 +5665,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5410,7 +5730,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5471,7 +5795,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5532,7 +5860,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5593,7 +5925,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5654,7 +5990,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5715,7 +6055,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5776,7 +6120,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5837,7 +6185,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5898,7 +6250,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5959,7 +6315,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6020,7 +6380,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6081,7 +6445,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6142,7 +6510,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6203,7 +6575,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6264,7 +6640,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6321,7 +6701,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6382,7 +6766,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6443,7 +6831,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6504,7 +6896,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6565,7 +6961,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6626,7 +7026,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6687,7 +7091,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6748,7 +7156,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6809,7 +7221,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6870,7 +7286,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6931,7 +7351,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6992,7 +7416,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7053,7 +7481,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7114,7 +7546,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7175,7 +7611,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7236,7 +7676,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7297,7 +7741,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7358,7 +7806,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7419,7 +7871,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7480,7 +7936,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7537,7 +7997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7598,7 +8062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7659,7 +8127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7720,7 +8192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7777,7 +8253,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7838,7 +8318,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7899,7 +8383,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7960,7 +8448,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8021,7 +8513,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8082,7 +8578,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8143,7 +8643,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8200,7 +8704,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8261,7 +8769,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8322,7 +8834,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8383,7 +8899,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8444,7 +8964,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8505,7 +9029,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8566,7 +9094,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8627,7 +9159,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8688,7 +9224,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8745,7 +9285,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8806,7 +9350,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8867,7 +9415,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8928,7 +9480,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8985,7 +9541,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9042,7 +9602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9103,7 +9667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9164,7 +9732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9225,7 +9797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9286,7 +9862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9347,7 +9927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9408,7 +9992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9469,7 +10057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9530,7 +10122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9591,7 +10187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9652,7 +10252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9713,7 +10317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9774,7 +10382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9835,7 +10447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9896,7 +10512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9957,7 +10577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10018,7 +10642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10079,7 +10707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10140,7 +10772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10201,7 +10837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10262,7 +10902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10323,7 +10967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10384,7 +11032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10445,7 +11097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10506,7 +11162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10567,7 +11227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10628,7 +11292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10689,7 +11357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10750,7 +11422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10811,7 +11487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10872,7 +11552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10929,7 +11613,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10990,7 +11678,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11051,7 +11743,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11112,7 +11808,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11173,7 +11873,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11230,7 +11934,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11291,7 +11999,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11352,7 +12064,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11413,7 +12129,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11474,7 +12194,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11535,7 +12259,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11596,7 +12324,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11657,7 +12389,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11718,7 +12454,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11779,7 +12519,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11840,7 +12584,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11901,7 +12649,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11962,7 +12714,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12023,7 +12779,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12084,7 +12844,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12145,7 +12909,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12202,7 +12970,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12263,7 +13035,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12324,7 +13100,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12381,7 +13161,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12442,7 +13226,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12503,7 +13291,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12564,7 +13356,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12625,7 +13421,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12686,7 +13486,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12747,7 +13551,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12808,7 +13616,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12869,7 +13681,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12930,7 +13746,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12991,7 +13811,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13052,7 +13876,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13113,7 +13941,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13174,7 +14006,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13231,7 +14067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13292,7 +14132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13353,7 +14197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13414,7 +14262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13475,7 +14327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13536,7 +14392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13597,7 +14457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13658,7 +14522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13719,7 +14587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13780,7 +14652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13841,7 +14717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13902,7 +14782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13959,7 +14843,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14020,7 +14908,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14077,7 +14969,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14138,7 +15034,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14199,7 +15099,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14260,7 +15164,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14321,7 +15229,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14382,7 +15294,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14443,7 +15359,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14504,7 +15424,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14565,7 +15489,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14626,7 +15554,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14687,7 +15619,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14748,7 +15684,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14809,7 +15749,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14870,7 +15814,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14931,7 +15879,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14992,7 +15944,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15053,7 +16009,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15110,7 +16070,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15171,7 +16135,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15228,7 +16196,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15289,7 +16261,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15350,7 +16326,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15411,7 +16391,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15472,7 +16456,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15533,7 +16521,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15594,7 +16586,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15655,7 +16651,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15716,7 +16716,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15777,7 +16781,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1457,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -1583,7 +1587,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -1901,7 +1909,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2034,7 +2042,11 @@
           <t>Hospital de Constitución</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -2290,7 +2302,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -2543,7 +2559,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2663,7 +2679,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3651,7 +3667,11 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -3712,7 +3732,11 @@
           <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -4225,7 +4249,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5138,7 +5162,11 @@
           <t>Hospital  Lonquimay</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -5196,7 +5224,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5524,7 +5552,11 @@
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -5647,7 +5679,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6232,7 +6264,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6297,7 +6329,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6690,7 +6722,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -6878,7 +6914,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7008,7 +7044,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7109,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,7 +7174,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,7 +7239,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7788,7 +7824,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,7 +7889,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7986,7 +8022,11 @@
           <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -8044,7 +8084,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8109,7 +8149,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8174,7 +8214,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8242,7 +8282,11 @@
           <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -8693,7 +8737,11 @@
           <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -8816,7 +8864,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9141,7 +9189,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9274,7 +9322,11 @@
           <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -9530,7 +9582,11 @@
           <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -9591,7 +9647,11 @@
           <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -10299,7 +10359,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10364,7 +10424,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10429,7 +10489,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10624,7 +10684,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10689,7 +10749,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11014,7 +11074,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11144,7 +11204,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11209,7 +11269,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11274,7 +11334,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11602,7 +11662,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -11923,7 +11987,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -12436,7 +12504,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12501,7 +12569,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12861,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>585-14-CM25</t>
+          <t>617807-913-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12886,17 +12954,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12920,7 +12988,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>23465.47</v>
+        <v>15667.62</v>
       </c>
     </row>
     <row r="194">
@@ -12959,7 +13027,11 @@
           <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -13052,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>617807-913-CM25</t>
+          <t>585-14-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13077,17 +13149,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13111,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>15667.62</v>
+        <v>23465.47</v>
       </c>
     </row>
     <row r="197">
@@ -13150,7 +13222,11 @@
           <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -13178,7 +13254,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1621-22-CM25</t>
+          <t>3779-5-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13198,22 +13274,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>69.130.401-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13237,7 +13313,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7742.05</v>
+        <v>387.31</v>
       </c>
     </row>
     <row r="199">
@@ -13568,7 +13644,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3779-5-CM25</t>
+          <t>1621-22-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13588,22 +13664,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.130.401-9</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13627,7 +13703,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>387.31</v>
+        <v>7742.05</v>
       </c>
     </row>
     <row r="205">
@@ -14056,7 +14132,11 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -14279,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1402-56-CM25</t>
+          <t>1407-15059-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14304,7 +14384,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -14314,7 +14394,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14338,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>10079.93</v>
+        <v>15119.9</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1407-15059-CM25</t>
+          <t>3385-8-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14369,17 +14449,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14403,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>15119.9</v>
+        <v>3109.66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3385-8-CM25</t>
+          <t>3481-15-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14434,17 +14514,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14468,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3109.66</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3481-15-CM25</t>
+          <t>2080-5931-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14499,17 +14579,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14533,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>499.91</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2080-5931-CM25</t>
+          <t>3428-19-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14564,17 +14644,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14598,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2015.99</v>
+        <v>3241.71</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3428-19-CM25</t>
+          <t>1968-131-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14629,12 +14709,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14663,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3241.71</v>
+        <v>36287.76</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1968-131-CM25</t>
+          <t>3374-1-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14694,17 +14774,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14728,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>36287.76</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3374-1-CM25</t>
+          <t>1402-56-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14759,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14793,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2015.99</v>
+        <v>10079.93</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>977274-1-CM25</t>
+          <t>3160-10-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14824,15 +14904,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.999.190-7</t>
+          <t>61.102.003-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -14854,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1996.46</v>
+        <v>2203.34</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1965-48-CM25</t>
+          <t>977274-1-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14885,17 +14969,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.999.190-7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14919,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>7985.85</v>
+        <v>1996.46</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1643-408-CM25</t>
+          <t>1965-48-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14950,15 +15034,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="I225" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -14980,7 +15068,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>10453.51</v>
+        <v>7985.85</v>
       </c>
     </row>
     <row r="226">
@@ -15051,7 +15139,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>752-40-CM25</t>
+          <t>1643-408-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15071,22 +15159,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15110,7 +15198,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1350.59</v>
+        <v>10453.51</v>
       </c>
     </row>
     <row r="228">
@@ -15201,7 +15289,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -15246,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3160-10-CM25</t>
+          <t>1371-7-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15271,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.102.003-1</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15305,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2203.34</v>
+        <v>609.72</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1371-7-CM25</t>
+          <t>1202512-8-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15336,17 +15424,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15370,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>609.72</v>
+        <v>9806.969999999999</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1202512-9-CM25</t>
+          <t>1391-174-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15401,17 +15489,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15435,13 +15523,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>284.4</v>
+        <v>7064</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1391-174-CM25</t>
+          <t>1978-128-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15461,17 +15549,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15500,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7064</v>
+        <v>43135.01</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1978-128-CM25</t>
+          <t>507428-2452-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15526,22 +15614,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15565,13 +15653,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>43135.01</v>
+        <v>26569.88</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>507428-2452-CM25</t>
+          <t>1628-11-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15596,17 +15684,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15630,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>26569.88</v>
+        <v>12109.71</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1628-11-CM25</t>
+          <t>1202512-9-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15661,17 +15749,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15695,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>12109.71</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1202512-8-CM25</t>
+          <t>622134-9-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15726,17 +15814,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.979.920-8</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15760,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>9806.969999999999</v>
+        <v>1438.03</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>622134-9-CM25</t>
+          <t>1288-40-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15791,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.979.920-8</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15825,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1438.03</v>
+        <v>38347.43</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1288-40-CM25</t>
+          <t>1529-28-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15856,17 +15944,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15890,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>38347.43</v>
+        <v>42326.03</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1529-28-CM25</t>
+          <t>2205-5-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15911,7 +15999,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15921,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15955,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>42326.03</v>
+        <v>5720.57</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2205-5-CM25</t>
+          <t>1681-64-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15986,17 +16074,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -16020,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>5720.57</v>
+        <v>36280.94</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1681-64-CM25</t>
+          <t>1681-63-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16059,7 +16147,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I242" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -16081,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>36280.94</v>
+        <v>24828.26</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1681-63-CM25</t>
+          <t>1057543-4819-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16107,22 +16199,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -16146,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>24828.26</v>
+        <v>57686.46</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057543-4819-CM25</t>
+          <t>652-33-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16172,20 +16264,24 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr"/>
+          <t>SERVICIO DE SALUD ARAUCO</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I244" t="inlineStr">
         <is>
           <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
@@ -16207,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>57686.46</v>
+        <v>27329.54</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>652-33-CM25</t>
+          <t>3431-13-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16238,17 +16334,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -16272,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>27329.54</v>
+        <v>4576.46</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3431-13-CM25</t>
+          <t>3311-8-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16303,17 +16399,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -16337,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4576.46</v>
+        <v>55662.34</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3311-8-CM25</t>
+          <t>1079596-5-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16368,17 +16464,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -16402,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>55662.34</v>
+        <v>21177.67</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1079596-5-CM25</t>
+          <t>3374-5-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16433,17 +16529,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16467,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>21177.67</v>
+        <v>4553.58</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3374-5-CM25</t>
+          <t>4100-1-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16498,17 +16594,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16532,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>4553.58</v>
+        <v>7516.07</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4100-1-CM25</t>
+          <t>1661-62-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16563,17 +16659,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16597,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>7516.07</v>
+        <v>16017.61</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1661-62-CM25</t>
+          <t>5827-10-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16628,17 +16724,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.977.660-7</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16662,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>16017.61</v>
+        <v>202.41</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5827-10-CM25</t>
+          <t>1057736-11-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16688,22 +16784,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.977.660-7</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16727,71 +16823,6 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>202.41</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>1057736-11-CM25</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>ene-2025</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>61.607.200-5</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M253" s="2" t="n">
         <v>4213.13</v>
       </c>
     </row>
